--- a/stockflow-crm/docs/use-cases/Casos_de_Uso_StockFlow.xlsx
+++ b/stockflow-crm/docs/use-cases/Casos_de_Uso_StockFlow.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,22 @@
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00374151"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -123,8 +137,13 @@
         <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -146,11 +165,69 @@
         <color rgb="009CA3AF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009CA3AF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009CA3AF"/>
+      </right>
+      <top style="thin">
+        <color rgb="009CA3AF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009CA3AF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009CA3AF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009CA3AF"/>
+      </right>
+      <top style="thin">
+        <color rgb="009CA3AF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009CA3AF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,6 +270,28 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -559,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -581,98 +680,106 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Sistema: Mini CRM para negocios de ecommerce  |  Proyecto Final de Grado — Técnico en Programación</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Módulo</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Nombre del UC</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Actor</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Precondiciones</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Flujo principal</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Flujo alternativo / Excepciones</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>Postcondiciones</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Autenticación</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="84" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B4" s="18" t="n"/>
+      <c r="C4" s="18" t="n"/>
+      <c r="D4" s="18" t="n"/>
+      <c r="E4" s="18" t="n"/>
+      <c r="F4" s="18" t="n"/>
+      <c r="G4" s="18" t="n"/>
+      <c r="H4" s="18" t="n"/>
+      <c r="I4" s="18" t="n"/>
+    </row>
+    <row r="5" ht="93.87096774193549" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>UC-01</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Autenticación</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Iniciar sesión</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Usuario (admin / operator)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>El usuario ingresa sus credenciales para acceder al sistema y obtener un token JWT.</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>El usuario tiene una cuenta registrada en el sistema.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>1. El usuario navega a la pantalla de login.
 2. Ingresa su email y contraseña.
@@ -682,159 +789,379 @@
 6. El sistema redirige al usuario al panel principal.</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>4a. Credenciales incorrectas: el sistema muestra «Email o contraseña inválidos» y no genera token.
-4b. Email no registrado: mismo mensaje de error (no se revela si el email existe).</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>4a. Credenciales incorrectas: el sistema muestra «Email o contraseña incorrectos» (HTTP 401). 4b. Correo sin verificar: HTTP 403 indicando que debe confirmar su dirección. 4c. Usuario desactivado: HTTP 403.</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>El usuario queda autenticado. El token JWT se almacena en el cliente y se incluye en cada petición posterior.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="6" ht="67.74193548387096" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>UC-02</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Autenticación</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Registrar usuario</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Dar de alta un usuario en la organización</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Se crea una cuenta de usuario nueva en el sistema con un rol determinado.</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>El email no debe estar registrado previamente.</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>1. El administrador realiza una petición POST a /auth/register con email, password y role.
-2. El sistema valida que el email tenga formato válido y la contraseña no esté vacía.
-3. El sistema hashea la contraseña con bcrypt.
-4. El sistema guarda el nuevo usuario en la base de datos.
-5. El sistema devuelve los datos del usuario creado (sin contraseña).</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>2a. Email duplicado: el sistema devuelve HTTP 400 «Email already registered».
-2b. Email con formato inválido: el sistema devuelve HTTP 422.</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>El usuario existe en la base de datos y puede iniciar sesión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Un administrador crea una cuenta para otro integrante de su equipo, dentro de su propia organización, asignándole rol de administrador u operador.</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>El usuario autenticado tiene rol 'admin'. El correo no está registrado en el sistema (la unicidad del correo es global).</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>1. El administrador entra al módulo «Usuarios». 2. Completa correo, nombre, teléfono, contraseña y rol. 3. El sistema realiza POST /users. 4. El usuario queda creado dentro de la organización del administrador.</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>2a. El usuario autenticado no es administrador: HTTP 403. 3a. Correo ya registrado: HTTP 400 con mensaje de negocio. 3b. Datos inválidos: HTTP 422 con el detalle por campo.</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>El nuevo usuario pertenece a la organización del administrador y puede iniciar sesión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="57.74193548387097" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>UC-03</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Autenticación</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Consultar usuario actual</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>El sistema devuelve los datos del usuario asociado al token JWT activo.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>El usuario tiene un token JWT válido y no expirado.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>1. El cliente realiza GET /auth/me incluyendo el token en el header Authorization.
 2. El sistema valida y decodifica el token.
 3. El sistema devuelve id, email y role del usuario.</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>2a. Token ausente o malformado: HTTP 401.
 2b. Token expirado: HTTP 401.</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>El cliente obtiene la información del usuario autenticado.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MÓDULO: Organizaciones y registro</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="18" t="n"/>
+      <c r="I8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="116.1290322580645" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>UC-20</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Organizaciones</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Registrar una organización (alta pública)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>Visitante (no autenticado)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>Alta pública del sistema: cualquier persona crea su propio CRM. Se genera una organización nueva con datos completamente aislados y quien la registra queda como su administrador. Es el único punto donde se obtiene el rol de administrador.</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>El correo no está registrado en el sistema.</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>1. El visitante entra a /signup. 2. Completa nombre de la organización, nombre y apellido, correo, teléfono y contraseña. 3. El sistema realiza POST /auth/signup. 4. Se crean la organización y su primer usuario con rol 'admin'. 5. Se genera un token de verificación y se envía el correo de confirmación. 6. Se muestra el aviso de revisar la bandeja de entrada.</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>3a. Correo ya registrado: HTTP 400 «Ya existe una cuenta con ese correo». 3b. Datos inválidos (contraseña débil, teléfono mal formado): HTTP 422 con el detalle por campo. 5a. Si el SMTP no está configurado, el enlace se escribe en el log del servidor y el alta igual se completa.</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>Existe una organización nueva con su administrador. La cuenta aún NO puede iniciar sesión hasta verificar el correo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="91.93548387096774" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>UC-21</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Organizaciones</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Verificar el correo electrónico</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Usuario recién registrado</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>El usuario confirma que es dueño de la dirección de correo declarada, activando así su cuenta para poder iniciar sesión.</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>Existe un usuario con un token de verificación vigente (24 horas).</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>1. El usuario abre el enlace recibido por correo. 2. El frontend toma el token de la URL y realiza GET /auth/verify-email?token=... 3. El sistema valida el token y su vencimiento. 4. Marca is_email_verified = true y anula el token. 5. Muestra la confirmación e invita a iniciar sesión.</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>3a. Token inexistente, ya usado o vencido: HTTP 400 «El enlace no es válido o ya venció», ofreciendo pedir uno nuevo.</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>La cuenta queda verificada y habilitada para iniciar sesión. El token de un solo uso queda invalidado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="68.38709677419355" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>UC-22</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Organizaciones</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Reenviar el enlace de verificación</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>Usuario no verificado</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>El usuario solicita un nuevo enlace de confirmación porque el anterior venció o no le llegó.</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>El correo corresponde a una cuenta existente sin verificar.</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>1. El usuario pide el reenvío desde la pantalla de inicio de sesión. 2. El sistema realiza POST /auth/resend-verification con el correo. 3. Se genera un token nuevo con 24 horas de validez. 4. Se envía el correo.</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>2a. Correo inexistente o ya verificado: por seguridad el sistema devuelve el mismo mensaje genérico, para no permitir averiguar qué correos están registrados.</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>El usuario recibe un enlace de verificación nuevo; el anterior deja de servir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MÓDULO: Usuarios</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="97.41935483870968" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>UC-23</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Usuarios</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Administrar los usuarios de la organización</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>El administrador cambia el rol de un integrante, lo activa o desactiva, o lo elimina de su organización.</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>El usuario autenticado tiene rol 'admin' y el usuario objetivo pertenece a su misma organización.</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>1. El administrador entra al módulo «Usuarios» y ve solo los de su organización. 2. Elige la acción: cambiar rol (PUT /users/{id}), activar/desactivar (PUT /users/{id}), o eliminar (DELETE /users/{id}). 3. El sistema valida que la organización no quede sin administradores activos. 4. Aplica el cambio.</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>1a. El usuario no es administrador: HTTP 403. 2a. Usuario de otra organización: HTTP 404 (no se revela su existencia). 3a. La acción dejaría a la organización sin ningún administrador activo: HTTP 400 explicando el motivo.</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>El usuario queda con el rol/estado nuevo o eliminado. La organización siempre conserva al menos un administrador activo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Productos</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="84" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="118.3870967741936" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>UC-04</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Crear producto</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>Se registra un nuevo producto en el catálogo de inventario.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>El usuario está autenticado. El SKU no existe en el sistema.</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>El usuario está autenticado. El SKU no existe dentro de su organización (dos organizaciones distintas sí pueden usar el mismo SKU).</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>1. El usuario completa el formulario: SKU, nombre, precio, stock inicial y stock mínimo.
 2. El usuario envía el formulario.
@@ -844,50 +1171,50 @@
 6. El sistema devuelve el producto creado con HTTP 201.</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>3a. SKU duplicado: HTTP 400 «SKU already exists».
 5a. Stock inicial = 0: no se genera movimiento de entrada.</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>El producto aparece en el inventario. Si tenía stock inicial, existe un movimiento de entrada asociado.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="16" ht="112.5806451612903" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>UC-05</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Actualizar producto</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>Se modifican los datos de un producto existente, incluyendo su stock.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>El producto existe en el sistema.</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>1. El usuario selecciona el producto y modifica los campos deseados (nombre, precio, stock, etc.).
 2. El usuario guarda los cambios.
@@ -896,50 +1223,50 @@
 5. El sistema devuelve el producto actualizado.</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>1a. Producto no encontrado: HTTP 404.
 4a. Stock no cambió: no se genera movimiento.</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>El producto queda actualizado. Si el stock cambió, hay un movimiento de ajuste en el historial.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="17" ht="70.96774193548387" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>UC-06</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Productos</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Eliminar producto</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Se elimina un producto del catálogo.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>El producto existe y no tiene movimientos de stock ni ítems de pedido asociados.</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>El producto existe, su stock es 0 y no tiene historial comercial (ni ítems de pedido ni movimientos originados en facturas).</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>1. El usuario selecciona el producto y confirma la eliminación.
 2. El sistema verifica que no existan registros relacionados.
@@ -947,57 +1274,111 @@
 4. El sistema devuelve HTTP 204.</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>2a. El producto tiene movimientos de stock asociados: HTTP 409 «Cannot delete product with stock history».
-1a. Producto no encontrado: HTTP 404.</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>2a. El producto tiene stock distinto de 0: HTTP 409 con el motivo. 2b. Tiene historial comercial: HTTP 409 explicando que no puede eliminarse. El listado expone 'can_delete' y el motivo para avisarlo antes de intentarlo.</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>El producto ya no existe en el sistema.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="18" ht="89.6774193548387" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>UC-24</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Gestionar artículos a granel (stock decimal)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Usuario autenticado</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Se distingue entre artículos que se venden por unidad y artículos a granel (kilos, litros, metros), que sí admiten cantidades con decimales.</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>El usuario está autenticado.</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>1. Al crear o editar el producto, el usuario marca «Admite stock decimal». 2. El sistema acepta cantidades fraccionarias para ese producto en facturas, pedidos y ajustes de stock. 3. Si el producto es por unidad, cualquier cantidad con decimales se rechaza con un mensaje claro.</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>3a. Cantidad decimal sobre un producto por unidad: HTTP 422 indicando que ese artículo solo admite cantidades enteras.</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>El stock refleja correctamente la unidad de medida del artículo (hasta 3 decimales para los productos a granel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Proveedores</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+    </row>
+    <row r="20" ht="87.74193548387096" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>UC-07</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>Crear proveedor</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>Se registra un nuevo proveedor en el sistema.</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>El usuario está autenticado.</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>1. El usuario completa el formulario: nombre (obligatorio), contacto (obligatorio), email (obligatorio), teléfono (opcional).
 2. El usuario envía el formulario.
@@ -1005,49 +1386,49 @@
 4. El sistema devuelve el proveedor creado con HTTP 201.</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>2a. Campos obligatorios faltantes: HTTP 422.</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>El proveedor queda disponible para asociar a facturas.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="98" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="21" ht="73.2258064516129" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>UC-08</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Proveedores</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>Actualizar / Eliminar proveedor</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>Se modifican o eliminan los datos de un proveedor existente.</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>El proveedor existe.</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>Actualizar:
 1. El usuario edita los campos del proveedor y guarda.
@@ -1057,56 +1438,64 @@
 2. El sistema elimina el proveedor y devuelve HTTP 204.</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>Proveedor no encontrado: HTTP 404 en ambos casos.</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>Los datos del proveedor quedan actualizados o el proveedor deja de existir.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Facturas</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="112" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>UC-09</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Facturas</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>Procesar factura con IA</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>El usuario sube un archivo de factura (PDF/JPG/PNG) y el sistema lo envía a Gemini 2.5 Flash para extraer los ítems automáticamente.</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>El usuario está autenticado. La clave GOOGLE_API_KEY está configurada. El archivo pesa ≤ 20 MB.</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>1. El usuario selecciona el archivo de factura.
 2. El usuario hace clic en «Analizar con IA».
@@ -1118,51 +1507,145 @@
 8. El sistema responde HTTP 201.</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>3a. Tipo MIME inválido: HTTP 415.
 5a. Gemini devuelve respuesta no parseable (JSON inválido): HTTP 422.
 5b. Servicio de Gemini saturado (free trial): el sistema puede mostrar error temporario; se recomienda reintentar en 10-30 segundos.</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>Se crea una factura en estado «Pendiente» con sus ítems en la base de datos.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="126" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="24" ht="83.87096774193549" customHeight="1">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>UC-25</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Facturas</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Rechazar un documento que no es una factura</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>Usuario autenticado</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Antes de extraer datos, la IA clasifica el documento subido. Si no es una factura ni un remito, se rechaza sin guardar nada, evitando datos basura.</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>El usuario está autenticado y subió un archivo válido (PDF/JPG/PNG/WEBP, máx. 20 MB).</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>1. El usuario sube el archivo. 2. El sistema valida el contenido real del archivo, no solo su extensión. 3. Gemini clasifica el documento. 4. Si no es una factura, devuelve el motivo. 5. El sistema responde con la explicación y NO crea ninguna factura ni ítem.</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>2a. Archivo que no es realmente una imagen/PDF pese a su extensión: HTTP 415. 2b. Archivo mayor a 20 MB: HTTP 413. 4a. Factura válida pero sin líneas detectables: se rechaza explicando que no se encontraron ítems.</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>No se persiste ninguna factura. El usuario recibe una explicación de por qué el documento no fue aceptado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="93.87096774193549" customHeight="1">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>UC-26</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>Facturas</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>Corregir u omitir líneas de una factura</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>Usuario autenticado</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>El usuario revisa lo que extrajo la IA y corrige manualmente descripción, cantidad y precio de cada línea, la asigna a un producto existente, crea uno nuevo, o la omite.</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>La factura existe en estado «Pendiente».</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>1. El sistema muestra las líneas con su nivel de confianza (alta/media/baja), resaltando las dudosas. 2. El usuario corrige los valores que hagan falta. 3. Asigna cada línea a un producto, crea uno nuevo, o la marca como omitida. 4. Puede salir y retomar después: la factura queda pendiente.</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>2a. Cantidad decimal en un producto por unidad: HTTP 422 con el motivo. 3a. Producto inexistente: HTTP 404 sin exponer identificadores internos. 3b. Error en una línea: la factura permanece pendiente y no se aplica nada (la confirmación es todo o nada).</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>Las líneas quedan corregidas y listas para confirmar. Las omitidas no afectarán el stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="150" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>UC-10</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>Facturas</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>Confirmar factura</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>El usuario revisa los ítems detectados, los asigna a productos del catálogo y confirma la factura, actualizando el stock.</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>La factura existe y está en estado «Pendiente».</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>1. El usuario revisa cada ítem de la factura.
 2. Para cada ítem el usuario asigna un producto existente o crea uno nuevo.
@@ -1175,107 +1658,115 @@
 9. El sistema actualiza el estado de la factura a «Confirmada».</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>Pre. Factura no encontrada: HTTP 400.
 Pre. Factura ya confirmada: HTTP 400.</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>La factura está «Confirmada». El stock de los productos fue actualizado. Los movimientos de entrada están registrados.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>UC-11</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>Facturas</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>Rechazar factura</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>El usuario rechaza una factura pendiente sin actualizar el stock.</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>La factura existe y está en estado «Pendiente».</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>1. El usuario hace clic en «Rechazar».
 2. El sistema actualiza el estado de la factura a «Rechazada».
 3. El sistema devuelve la factura actualizada.</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>Pre. Factura no encontrada: HTTP 400.
 Pre. Factura ya rechazada: HTTP 400.</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>La factura queda en estado «Rechazada». El stock no fue modificado.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Clientes</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="154" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+    </row>
+    <row r="29" ht="109.0322580645161" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>UC-12</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>Crear / Actualizar / Eliminar cliente</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>CRUD completo de clientes del negocio.</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>El usuario está autenticado.</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>Crear:
 1. El usuario completa nombre, email, teléfono y (opcionalmente) dirección.
@@ -1288,106 +1779,114 @@
 2. El sistema elimina el cliente y devuelve HTTP 204.</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>Crear — email inválido: HTTP 422.
 Actualizar / Eliminar — cliente no encontrado: HTTP 404.</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>El cliente existe/está actualizado/fue eliminado del sistema.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="30" ht="66.77419354838709" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>UC-13</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>Ver historial de pedidos del cliente</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>Se consulta el historial completo de pedidos de un cliente con totales.</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>El cliente existe.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>1. El usuario hace clic en el ícono de historial del cliente.
 2. El sistema devuelve la lista de pedidos del cliente con estado, fecha y total.
 3. Si el cliente no tiene pedidos, se devuelve una lista vacía.</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>Cliente no encontrado: HTTP 404.</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>El usuario puede ver el historial comercial del cliente.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Pedidos</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
+      <c r="I31" s="18" t="n"/>
+    </row>
+    <row r="32" ht="63.87096774193548" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>UC-14</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>Crear pedido</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>Se crea un pedido vacío en estado «Pendiente» para un cliente.</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>El cliente existe en el sistema.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>1. El usuario selecciona el cliente en el formulario.
 2. El usuario hace clic en «Crear».
@@ -1395,49 +1894,49 @@
 4. El sistema devuelve el pedido con HTTP 201.</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>Cliente no encontrado: HTTP 400.</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>Existe un pedido vacío en estado «Pendiente» para el cliente.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="70" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="33" ht="94.83870967741935" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>UC-15</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>Agregar ítem al pedido</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>Se añade un producto con cantidad y precio unitario a un pedido pendiente.</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>El pedido existe en estado «Pendiente». El producto está activo.</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>1. El usuario selecciona el producto, ingresa la cantidad y el precio unitario.
 2. El usuario hace clic en «Agregar».
@@ -1446,51 +1945,51 @@
 5. El sistema devuelve el pedido actualizado con el nuevo total.</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>3a. Stock insuficiente: HTTP 400 «Insufficient stock».
 3b. Producto inactivo: HTTP 400.
 Pre. Pedido no encontrado: HTTP 400.</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>El ítem aparece en el pedido. El total del pedido se actualizó.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="154" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="34" ht="150" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>UC-16</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>Avanzar estado del pedido</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>El pedido avanza un paso en el flujo: Pendiente → Procesando → Enviado → Entregado.</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>El pedido existe. El pedido no está en estado «Entregado».</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>1. El usuario hace clic en «Avanzar».
 Pendiente → Procesando:
@@ -1505,107 +2004,115 @@
   a. El sistema actualiza el estado. Envía email al cliente.</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>Pre. Pedido sin ítems al avanzar a Procesando: HTTP 400 «Order has no items».
 b. Stock insuficiente en el momento de procesar: HTTP 400. El pedido permanece en «Pendiente».
 Pre. Pedido ya «Entregado»: HTTP 400.</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>El pedido avanzó de estado. Si pasó a «Procesando», el stock fue descontado y hay movimientos de salida.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>UC-17</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Pedidos</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>Eliminar pedido</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>Se elimina un pedido que aún no fue procesado.</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>El pedido existe y está en estado «Pendiente».</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>1. El usuario confirma la eliminación.
 2. El sistema elimina el pedido y sus ítems.
 3. El sistema devuelve HTTP 204.</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>Pedido en estado ≠ «Pendiente»: HTTP 400.</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I35" s="20" t="inlineStr">
         <is>
           <t>El pedido ya no existe. El stock no fue afectado.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  MÓDULO: Movimientos de Stock</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="70" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="18" t="n"/>
+      <c r="I36" s="18" t="n"/>
+    </row>
+    <row r="37" ht="119.6774193548387" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>UC-18</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>Consultar movimientos de stock</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>El usuario puede ver y filtrar el historial completo de movimientos de stock (solo lectura).</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>El usuario está autenticado.</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t>1. El usuario navega al módulo «Movimientos».
 2. El sistema devuelve la lista de movimientos ordenada por fecha descendente.
@@ -1614,74 +2121,186 @@
 5. El usuario puede ver el detalle de un movimiento (factura o pedido vinculado).</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>Movimiento no encontrado en detalle: HTTP 404.</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I37" s="20" t="inlineStr">
         <is>
           <t>El usuario puede auditar el historial de stock.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="38" ht="75.16129032258064" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>UC-19</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Movimientos de Stock</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>Filtrar y paginar movimientos</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>Usuario autenticado</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E38" s="20" t="inlineStr">
         <is>
           <t>El usuario aplica filtros combinados para acotar el historial de movimientos.</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F38" s="20" t="inlineStr">
         <is>
           <t>Existen movimientos de stock registrados.</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
         <is>
           <t>1. El usuario selecciona filtros: tipo de movimiento, producto específico y/o rango de fechas.
 2. El usuario puede configurar el límite de resultados por página.
 3. El sistema devuelve los movimientos que cumplen todos los criterios.</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr">
         <is>
           <t>Sin resultados: se devuelve una lista vacía (HTTP 200).</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I38" s="20" t="inlineStr">
         <is>
           <t>El usuario obtiene el subconjunto de movimientos solicitado.</t>
         </is>
       </c>
     </row>
+    <row r="39" ht="56" customHeight="1">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>UC-27</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Movimientos de Stock</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>Validar el rango de fechas del filtro</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>Usuario autenticado</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>Si el usuario indica un rango de fechas invertido, el sistema lo explica en lugar de devolver una lista vacía sin motivo.</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>El usuario está en el módulo «Movimientos».</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>1. El usuario indica fecha desde y fecha hasta. 2. El sistema valida que 'desde' no sea posterior a 'hasta'. 3. Si es válido, aplica el filtro.</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>2a. Rango invertido: HTTP 422 con un mensaje explicativo señalando el campo, en vez de una lista vacía ambigua.</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>El usuario obtiene los movimientos del rango, o un error claro que le permite corregir el filtro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MÓDULO: Multi-tenancy</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="18" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="18" t="n"/>
+      <c r="I40" s="18" t="n"/>
+    </row>
+    <row r="41" ht="68.38709677419355" customHeight="1">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>UC-28</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Multi-tenancy</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>Aislamiento de datos entre organizaciones</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>Usuario autenticado</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>Requisito transversal: ningún usuario puede ver ni modificar datos de otra organización. Aplica a productos, proveedores, clientes, pedidos, facturas y movimientos de stock.</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>Existen al menos dos organizaciones con datos propios.</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>1. El usuario realiza cualquier consulta de la API con su token. 2. El sistema resuelve su organización a partir del token. 3. Toda consulta se filtra por esa organización. 4. Solo se devuelven sus propios datos.</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>2a. Se solicita un recurso de otra organización por su id: HTTP 404, igual que si no existiera (no se revela su existencia). 2b. Se intenta modificar o confirmar un recurso ajeno: HTTP 404.</t>
+        </is>
+      </c>
+      <c r="I41" s="22" t="inlineStr">
+        <is>
+          <t>Cada organización solo accede a sus propios datos. La existencia de recursos ajenos nunca se filtra.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A15:I15"/>
+  <mergeCells count="12">
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A14:I14"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A40:I40"/>
     <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A31:I31"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A4:I4"/>
